--- a/data/synthetic/messy_foyle/bookings Jan-May 2026.xlsx
+++ b/data/synthetic/messy_foyle/bookings Jan-May 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pre-arrival logistics</t>
+          <t>document collection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arrival</t>
+          <t>Pre-Arrival Logistics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -620,17 +620,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B-2026-002</t>
+          <t>B-2026-001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>request received</t>
+          <t>arrival</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLACEMENT OFFER</t>
+          <t>REQUEST RECEIVED</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placement Re-allocation </t>
+          <t xml:space="preserve">Placement Offer </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24/01/2026</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>25/01/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>invoice issued</t>
+          <t>placement offer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRE-ARRIVAL LOGISTICS</t>
+          <t xml:space="preserve">Invoice Issued </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARRIVAL</t>
+          <t>DOCUMENT COLLECTION</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,24 +802,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B-2026-003</t>
+          <t>B-2026-002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>request received</t>
+          <t>PRE-ARRIVAL LOGISTICS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,29 +829,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B-2026-003</t>
+          <t>B-2026-002</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>placement offer</t>
+          <t>arrival</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BOOKING CONFIRMED</t>
+          <t>request received</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INVOICE ISSUED</t>
+          <t>PLACEMENT OFFER</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>08/02/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Document Re-request</t>
+          <t>BOOKING CONFIRMED</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>waiting on family</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Arrival Logistics </t>
+          <t>invoice issued</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15/02/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -976,66 +976,66 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arrival</t>
+          <t xml:space="preserve">Document Collection </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B-2026-004</t>
+          <t>B-2026-003</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request Received </t>
+          <t>Document Collection</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B-2026-004</t>
+          <t>B-2026-003</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placement Offer </t>
+          <t xml:space="preserve">Pre-Arrival Logistics </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>21/02/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1052,17 +1052,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B-2026-004</t>
+          <t>B-2026-003</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BOOKING CONFIRMED</t>
+          <t xml:space="preserve">Arrival </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>INVOICE ISSUED</t>
+          <t>REQUEST RECEIVED</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Arrival Logistics </t>
+          <t>PLACEMENT OFFER</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>18/02/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Arrival</t>
+          <t xml:space="preserve">Booking Confirmed </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,17 +1160,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B-2026-005</t>
+          <t>B-2026-004</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>REQUEST RECEIVED</t>
+          <t>Invoice Issued</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,24 +1180,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B-2026-005</t>
+          <t>B-2026-004</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Placement Offer</t>
+          <t>document collection</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,24 +1207,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B-2026-005</t>
+          <t>B-2026-004</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking Confirmed </t>
+          <t>PRE-ARRIVAL LOGISTICS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1241,27 +1241,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B-2026-005</t>
+          <t>B-2026-004</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice Issued </t>
+          <t>ARRIVAL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pre-Arrival Logistics</t>
+          <t>Request Received</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,120 +1300,120 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrival </t>
+          <t>Placement Offer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B-2026-006</t>
+          <t>B-2026-005</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request Received </t>
+          <t>booking confirmed</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B-2026-006</t>
+          <t>B-2026-005</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Placement Offer</t>
+          <t>invoice issued</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B-2026-006</t>
+          <t>B-2026-005</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placement Re-allocation </t>
+          <t>Document Collection</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B-2026-006</t>
+          <t>B-2026-005</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>booking confirmed</t>
+          <t>Pre-Arrival Logistics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>28/03/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1423,24 +1423,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B-2026-006</t>
+          <t>B-2026-005</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INVOICE ISSUED</t>
+          <t>ARRIVAL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pre-arrival logistics</t>
+          <t>REQUEST RECEIVED</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22/03/2026</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>arrival</t>
+          <t>Placement Offer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,71 +1511,71 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B-2026-007</t>
+          <t>B-2026-006</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request Received </t>
+          <t>BOOKING CONFIRMED</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B-2026-007</t>
+          <t>B-2026-006</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placement Offer </t>
+          <t>PLACEMENT OFFER</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>29/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B-2026-007</t>
+          <t>B-2026-006</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking Confirmed </t>
+          <t>invoice issued</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1585,88 +1585,88 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B-2026-007</t>
+          <t>B-2026-006</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Invoice Issued</t>
+          <t xml:space="preserve">Document Collection </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>28/03/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B-2026-007</t>
+          <t>B-2026-006</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Document Re-request </t>
+          <t xml:space="preserve">Pre-Arrival Logistics </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B-2026-007</t>
+          <t>B-2026-006</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pre-Arrival Logistics</t>
+          <t xml:space="preserve">Arrival </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1678,174 +1678,174 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ARRIVAL</t>
+          <t>Request Received</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B-2026-008</t>
+          <t>B-2026-007</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>request received</t>
+          <t xml:space="preserve">Placement Offer </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B-2026-008</t>
+          <t>B-2026-007</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>placement offer</t>
+          <t>booking confirmed</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>28/03/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B-2026-008</t>
+          <t>B-2026-007</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Booking Confirmed</t>
+          <t>INVOICE ISSUED</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B-2026-008</t>
+          <t>B-2026-007</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>invoice issued</t>
+          <t>document collection</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B-2026-008</t>
+          <t>B-2026-007</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Arrival Logistics </t>
+          <t xml:space="preserve">Document Collection </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>chased 2x</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B-2026-008</t>
+          <t>B-2026-007</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>arrival</t>
+          <t>pre-arrival logistics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1862,76 +1862,76 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B-2026-009</t>
+          <t>B-2026-007</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>REQUEST RECEIVED</t>
+          <t xml:space="preserve">Arrival </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B-2026-009</t>
+          <t>B-2026-008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Placement Offer</t>
+          <t>Request Received</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B-2026-009</t>
+          <t>B-2026-008</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Booking Confirmed</t>
+          <t>PLACEMENT OFFER</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1943,22 +1943,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B-2026-009</t>
+          <t>B-2026-008</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>invoice issued</t>
+          <t>BOOKING CONFIRMED</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1970,71 +1970,71 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B-2026-009</t>
+          <t>B-2026-008</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PRE-ARRIVAL LOGISTICS</t>
+          <t>Invoice Issued</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B-2026-009</t>
+          <t>B-2026-008</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrival </t>
+          <t>document collection</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B-2026-010</t>
+          <t>B-2026-008</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t>PRE-ARRIVAL LOGISTICS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2044,24 +2044,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B-2026-010</t>
+          <t>B-2026-008</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PLACEMENT OFFER</t>
+          <t>ARRIVAL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2071,115 +2071,385 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B-2026-010</t>
+          <t>B-2026-009</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking Confirmed </t>
+          <t>Request Received</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B-2026-010</t>
+          <t>B-2026-009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>invoice issued</t>
+          <t>placement offer</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B-2026-010</t>
+          <t>B-2026-009</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pre-Arrival Logistics</t>
+          <t>BOOKING CONFIRMED</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>B-2026-009</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Invoice Issued</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>B-2026-009</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DOCUMENT COLLECTION</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sean Doyle</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>B-2026-009</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>pre-arrival logistics</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B-2026-009</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ARRIVAL</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sean Doyle</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>B-2026-010</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Sean Doyle</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Request Received</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>B-2026-010</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placement Offer </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B-2026-010</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>booking confirmed</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B-2026-010</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>invoice issued</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Completed ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B-2026-010</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>document collection</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B-2026-010</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PRE-ARRIVAL LOGISTICS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B-2026-010</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arrival </t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
     </row>

--- a/data/synthetic/messy_foyle/bookings Jan-May 2026.xlsx
+++ b/data/synthetic/messy_foyle/bookings Jan-May 2026.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>18/01/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>08/02/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>15/02/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25/01/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>08/02/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>14/02/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>14/02/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>21/02/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21/02/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>08/03/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>28/03/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>28/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>28/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>28/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
